--- a/data/trans_dic/IP31KM05_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,33; 86,33</t>
+          <t>69,44; 87,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,35; 87,24</t>
+          <t>64,23; 85,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,09; 84,15</t>
+          <t>71,05; 85,74</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,0; 85,38</t>
+          <t>79,6; 85,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,43; 85,23</t>
+          <t>77,51; 84,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,18; 84,51</t>
+          <t>79,51; 84,49</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,97; 84,36</t>
+          <t>75,52; 86,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,47; 87,0</t>
+          <t>72,88; 84,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,1; 84,24</t>
+          <t>76,45; 84,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,5; 83,76</t>
+          <t>79,69; 84,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,52; 84,14</t>
+          <t>77,42; 82,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,04; 83,24</t>
+          <t>79,33; 83,26</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40667</t>
+          <t>43307</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45928</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86594</t>
+          <t>78551</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33472; 46357</t>
+          <t>37297; 47257</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38711; 50902</t>
+          <t>29485; 39366</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76290; 94282</t>
+          <t>70782; 85412</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>506</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>368267</t>
+          <t>386404</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>415290</t>
+          <t>342674</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>783557</t>
+          <t>729079</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>352441; 385789</t>
+          <t>371272; 400446</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>396271; 430646</t>
+          <t>329172; 356757</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>757845; 808804</t>
+          <t>708541; 752923</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>115926</t>
+          <t>136299</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>147544</t>
+          <t>116940</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263469</t>
+          <t>253238</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>106668; 123320</t>
+          <t>125883; 144330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136706; 157584</t>
+          <t>107229; 124330</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>249097; 275731</t>
+          <t>239932; 264195</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>733</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>524861</t>
+          <t>566010</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>494858</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1133621</t>
+          <t>1060868</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>505067; 545859</t>
+          <t>547310; 583530</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>584740; 626642</t>
+          <t>478203; 511597</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1103734; 1162372</t>
+          <t>1034834; 1086219</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM05_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumen pescados con regularidad (por lo menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>80,62%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>76,77%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>69,44; 87,98</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>64,23; 85,76</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>71,05; 85,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>82,84%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>80,69%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>81,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>79,6; 85,85</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>77,51; 84,01</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>79,51; 84,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>81,77%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>79,48%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>75,52; 86,59</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>72,88; 84,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>76,45; 84,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>79,69; 84,96</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>77,42; 82,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>79,33; 83,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8062450424080924</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7677451366315983</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7885042419850096</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>43307</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>35243</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>78551</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.6943575292739382</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6423024009800137</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.710515546176171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>37297; 47257</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29485; 39366</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>70782; 85412</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.8797753267543121</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.857551183269513</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.8573754153743602</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8284414079574411</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8069270252235043</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.818188304312408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>386404</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>342674</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>729079</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7959993558303392</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.7751325899667026</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.7951391195511817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>371272; 400446</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>329172; 356757</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>708541; 752923</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8585465855872476</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8400889041381135</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.844946574050552</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8176962159344947</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7947521530512448</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8069386930064842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>136299</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>116940</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>253238</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7552107727332644</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7287524101216122</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.7645412040212893</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>125883; 144330</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>107229; 124330</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>239932; 264195</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8658774450168192</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8449774846882994</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8418549846765073</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.824097730611566</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8011151747786341</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8132152475066143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>566010</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>494858</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1060868</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7968715016082131</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7741540204684438</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7932588623823255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>547310; 583530</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>478203; 511597</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1034834; 1086219</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8496062956783793</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8282134551037365</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8326486538088512</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumen pescados con regularidad (por lo menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>43307</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>35243</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>78551</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>37297</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>29485</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>70782</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>47257</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>39366</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>85412</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>518</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>506</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>386404</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>342674</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>729079</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>371272</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>329172</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>708541</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>400446</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>356757</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>752923</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>194</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>136299</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>116940</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>253238</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>125883</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>107229</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>239932</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>144330</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>124330</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>264195</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>772</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>733</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>566010</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>494858</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1060868</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>547310</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>478203</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1034834</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>583530</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>511597</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1086219</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>